--- a/Review By Myself.xlsx
+++ b/Review By Myself.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\research work\git updates\RESEARCH-MENTAL-HEALTH-EVALUATOR-AND-RETALIATION-MODEL\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3598BE2-7442-4EE4-BDD9-6DC0349A3188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,9 +24,56 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Privacy Model</t>
+  </si>
+  <si>
+    <t>Detection Scope</t>
+  </si>
+  <si>
+    <t>Validation</t>
+  </si>
+  <si>
+    <t>Standards</t>
+  </si>
+  <si>
+    <t>Limitations</t>
+  </si>
+  <si>
+    <t>Industry Fit</t>
+  </si>
+  <si>
+    <t>The paper presents Sentinel as a privacy-preserving edge-AI architecture for proactive mental-health anomaly detection. The title indicates that inference is intended to occur at or near the data source through edge computing, with possible cloud involvement for coordination, storage, or model management; specific device types, data flows, cloud components, and deployment topology are not reported.</t>
+  </si>
+  <si>
+    <t>The architecture is explicitly privacy-preserving, and its edge-AI design suggests that sensitive mental-health data may be processed locally rather than transferred wholesale to a central service. However, the available information does not establish whether Sentinel uses on-device inference, federated learning, encryption, consent management, data minimization, differential privacy, access controls, or formal privacy guarantees; the associated privacy assumptions are therefore unclear.</t>
+  </si>
+  <si>
+    <t>Sentinel is intended to detect mental-health anomalies proactively. The specific conditions, behavioral or physiological signals, anomaly definitions, target population, alert thresholds, and intended clinical or wellness use case are not identified.</t>
+  </si>
+  <si>
+    <t>Study design, datasets, sample size, baselines, evaluation metrics, and validation setting are not reported. It is therefore not possible to determine whether Sentinel was evaluated in a laboratory, simulated, retrospective, or real-world deployment, or whether detection performance and privacy overhead were empirically demonstrated.</t>
+  </si>
+  <si>
+    <t>No clinical, security, machine-learning, software-engineering, interoperability, or regulatory standards are identified in the available material. Alignment with frameworks such as medical-device guidance, health-data regulations, secure-development practices, or responsible-AI principles remains undetermined.</t>
+  </si>
+  <si>
+    <t>The available description does not provide explicit limitations, failure analyses, or unresolved technical and clinical risks. Important open issues include false positives and false negatives, concept drift, ambiguous anomaly definitions, model bias across populations, escalation and human oversight, privacy leakage from edge outputs or updates, device compromise, and the absence of reported empirical validation.</t>
+  </si>
+  <si>
+    <t>The proposed edge-AI orientation is potentially relevant to privacy-sensitive mental-health applications by reducing dependence on centralized data transfer and supporting near-real-time detection. Production readiness cannot be assessed because device requirements, interoperability, scalability, model-update and maintenance processes, monitoring, cybersecurity controls, integration with clinical workflows, alert governance, regulatory classification, and operational costs are not described.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +81,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1C1917"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF57534E"/>
+      <name val="Inter"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -45,12 +115,72 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +460,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.28515625" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="5" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="301.5" customHeight="1" thickBot="1">
+      <c r="A2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="4"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>